--- a/demo_parameters.xlsx
+++ b/demo_parameters.xlsx
@@ -428,7 +428,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.84"/>
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>6</v>
@@ -504,7 +504,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>38.5</v>
+        <v>-61.5</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -524,7 +524,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>20.3</v>
+        <v>-19.7</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>6</v>

--- a/demo_parameters.xlsx
+++ b/demo_parameters.xlsx
@@ -199,7 +199,7 @@
     <t xml:space="preserve">*Solenoid field on axis defined by B = B0.5 sin( pi z/L) + B0 sin(2 pi z/L) + B1 sin(4 pi z/L) + B2 sin (6 pi z/L)</t>
   </si>
   <si>
-    <t xml:space="preserve">** Field on axis in RF cavity defined by E = E0 sin(2 pi f t + phi); adjacent cavities have phi offset by 180 degrees</t>
+    <t xml:space="preserve">** Field on axis in RF cavity defined by E = E0 sin(2 pi f t + phi); adjacent RF cells in the 3 cell cavity have phi offset by 180 degrees</t>
   </si>
 </sst>
 </file>
@@ -428,7 +428,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.84"/>

--- a/demo_parameters.xlsx
+++ b/demo_parameters.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -305,48 +305,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -422,597 +426,703 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="3" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>188.6</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="G3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>-61.5</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="C5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>81.6</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="G5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>-19.7</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>81.6</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="C7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>0.704</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="6" t="s">
+    <row r="8" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6" t="s">
+      <c r="C14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>0.025</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="7" t="n">
         <v>0.02</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="6" t="s">
+      <c r="G18" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>285</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6" t="s">
+      <c r="C22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="6"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="7" t="n">
         <v>268</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="C23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="C24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="10" t="n">
         <v>211</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="C25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="C26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="C27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="7" t="n">
         <v>328.43</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="E30" s="10"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="7" t="n">
         <v>185</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="5"/>
+      <c r="C31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C37" s="6"/>
+      <c r="C37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="11" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="11" t="s">
         <v>59</v>
       </c>
     </row>
